--- a/apps/static/PlantillaTransferenciasDepositos.xlsx
+++ b/apps/static/PlantillaTransferenciasDepositos.xlsx
@@ -443,15 +443,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -465,22 +467,30 @@
           <t>R1001A01</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>A0201001</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>ARTICULO-001</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="n">
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>ARTICULO-VIEJO</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>P0401001</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>ARTICULO-NUEVO</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -495,23 +505,69 @@
           <t>A0501001</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>P0401001</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>ARTICULO-002</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="D2" s="2" t="n">
         <v>2</v>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>A0201001</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>ARTICULO-002</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>R1002A01</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>ARTICULO-VIEJO2</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>R1002A01</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>ARTICULO-NUEVO2</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -525,7 +581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A28"/>
+  <dimension ref="A1:A45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="78" customWidth="1" min="1" max="1"/>
@@ -575,137 +631,252 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  C - Depósito de destino     (04, 06, 10 o 20)</t>
+          <t xml:space="preserve">  C - Artículo de origen      (el código que se da de BAJA)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  D - Ubicación de destino    (código de ubicación del WMS)</t>
+          <t xml:space="preserve">  D - Cantidad de baja        (entero POSITIVO)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  E - Código de artículo</t>
+          <t xml:space="preserve">  E - Depósito de destino     (04, 06, 10 o 20)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  F - Cantidad                (entero POSITIVO)</t>
+          <t xml:space="preserve">  F - Ubicación de destino    (código de ubicación del WMS)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr"/>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  G - Artículo de destino     (el código que se da de ALTA)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Depósitos habilitados</t>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  H - Cantidad de alta        (entero POSITIVO, igual a la de baja)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  04 - OUTLET</t>
-        </is>
-      </c>
+      <c r="A14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  06 - FALLAS</t>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Transferencia o recodificación</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  10 - RECODIFICACIONES</t>
+          <t xml:space="preserve">  * Si el artículo de destino es el MISMO código, es una transferencia:</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  20 - ARREGLOS PRODUCCION</t>
+          <t xml:space="preserve">    el artículo se mueve de una ubicación a otra.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr"/>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * Si es un código DISTINTO, es una recodificación: se da de baja el</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Cosas importantes</t>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    código viejo y de alta el nuevo.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * La cantidad SIEMPRE va positiva. El sentido lo dan las columnas</t>
+          <t xml:space="preserve">  * Se puede recodificar sin moverse de estante: mismo depósito y misma</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">    de origen y destino, no el signo.</t>
+          <t xml:space="preserve">    ubicación, cambiando solo el código.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  * Cada ubicación tiene que pertenecer al depósito que declarás en la</t>
-        </is>
-      </c>
+      <c r="A22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    misma fila. Si no coincide, la fila se rechaza.</t>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Depósitos habilitados</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * Los códigos de depósito llevan dos dígitos ("04", no "4"). La</t>
+          <t xml:space="preserve">  04 - OUTLET</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">    columna está formateada como texto para que Excel no coma el cero.</t>
+          <t xml:space="preserve">  06 - FALLAS</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * Si UNA fila falla la validación, NO se aplica nada del lote.</t>
+          <t xml:space="preserve">  10 - RECODIFICACIONES</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">  20 - ARREGLOS PRODUCCION</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Cosas importantes</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * Las cantidades SIEMPRE van positivas. El sentido lo dan las columnas</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    de origen y destino, no el signo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * Las dos cantidades tienen que ser IGUALES. Se piden por separado</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    como control: si tipeás mal una, la fila se rechaza en vez de mover</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    una cantidad equivocada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * Si el artículo de destino maneja partidas y no tiene ninguna partida</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    de referencia, la fila se rechaza.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * Si el artículo no tiene stock en el depósito que pusiste, la pantalla</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    te va a decir en cuál de los 4 sí está y te deja corregirlo con un clic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * Cada ubicación tiene que pertenecer al depósito que declarás en la</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    misma fila. Si no coincide, la fila se rechaza.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * Los códigos de depósito llevan dos dígitos ("04", no "4"). La</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    columna está formateada como texto para que Excel no coma el cero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * Si UNA fila falla la validación, NO se aplica nada del lote.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">    Se corrigen todas las filas marcadas y se vuelve a validar.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  * Borrá las filas de ejemplo (en gris) antes de cargar las tuyas.</t>
         </is>
